--- a/TPMA 課程管理系統資料庫規劃.xlsx
+++ b/TPMA 課程管理系統資料庫規劃.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/544b8d222a0c7139/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEB\tpma-course-registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{111F7071-731D-41DB-995B-DC957F5601E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63E9700-0A17-426E-99E7-433C95D987EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CC97D7-C6A3-453D-9EC9-72FF710D6796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2550" yWindow="4185" windowWidth="24270" windowHeight="11295" xr2:uid="{0F77293A-3451-41FC-851F-0442166EED0A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F77293A-3451-41FC-851F-0442166EED0A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,92 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E8AEA38C-695D-476C-B251-A4AD4F985225}</author>
+    <author>tc={BB73BC85-84DA-4531-8D11-2FEC40B6C6D8}</author>
+    <author>tc={9BAD3334-5BDE-4AD4-BD15-5631AF5FE627}</author>
+    <author>tc={C840BA3F-13DF-4C3B-B55C-EE68DB23CE7E}</author>
+    <author>tc={56566999-2D7A-450F-8573-8D9F8B382CCF}</author>
+    <author>tc={C6DC1EE6-FFFC-4540-8679-DE132156B117}</author>
+    <author>tc={EE33FCBE-1363-47FA-91CA-DAC4F880F21B}</author>
+    <author>tc={AB3E87E4-B2AE-4BF6-8465-D710692CC0A6}</author>
+  </authors>
+  <commentList>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{E8AEA38C-695D-476C-B251-A4AD4F985225}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    自動寫入：未付款</t>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="1" shapeId="0" xr:uid="{BB73BC85-84DA-4531-8D11-2FEC40B6C6D8}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    自動寫入：待合帳</t>
+      </text>
+    </comment>
+    <comment ref="G26" authorId="2" shapeId="0" xr:uid="{9BAD3334-5BDE-4AD4-BD15-5631AF5FE627}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    自動寫入：待發證</t>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="3" shapeId="0" xr:uid="{C840BA3F-13DF-4C3B-B55C-EE68DB23CE7E}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    自動寫入：待發證</t>
+      </text>
+    </comment>
+    <comment ref="A29" authorId="4" shapeId="0" xr:uid="{56566999-2D7A-450F-8573-8D9F8B382CCF}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    1.待開立
+2.已自動
+3.已手動
+4.已寄出</t>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="5" shapeId="0" xr:uid="{C6DC1EE6-FFFC-4540-8679-DE132156B117}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    待開立</t>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="6" shapeId="0" xr:uid="{EE33FCBE-1363-47FA-91CA-DAC4F880F21B}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    自動寫入：已自動</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="7" shapeId="0" xr:uid="{AB3E87E4-B2AE-4BF6-8465-D710692CC0A6}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    自動寫入：已手動、已寄出</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="135">
   <si>
     <t>英文欄位名稱</t>
   </si>
@@ -158,322 +242,345 @@
     <t>匯款帳號</t>
   </si>
   <si>
+    <t>DATETIME DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>remit_amount</t>
+  </si>
+  <si>
+    <t>DECIMAL(10,2) DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>匯款金額</t>
+  </si>
+  <si>
+    <t>VARCHAR(20) NOT NULL DEFAULT 'electronic'</t>
+  </si>
+  <si>
+    <t>VARCHAR(20) NOT NULL DEFAULT 'pending'</t>
+  </si>
+  <si>
+    <t>報名編號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名時間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承辦人姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承辦人電子郵件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資訊來源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>匯款時間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>學員mail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>學員手機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司抬頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司統編</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司電話</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收據方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名管理系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程管理系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報名狀態查詢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測驗卷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料匯入系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動寫入</t>
+  </si>
+  <si>
+    <t>唯讀</t>
+  </si>
+  <si>
+    <t>只寫入</t>
+  </si>
+  <si>
+    <t>可讀可寫</t>
+  </si>
+  <si>
+    <t>唯讀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動寫入、可查詢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測驗成績</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR(20) NOT NULL</t>
+  </si>
+  <si>
+    <t>INT NOT NULL DEFAULT 0</t>
+  </si>
+  <si>
+    <t>講師代碼</t>
+  </si>
+  <si>
+    <t>講師代碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>講師姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>職稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯示順序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>course_code</t>
+  </si>
+  <si>
+    <t>VARCHAR(50) NOT NULL</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>課程類別</t>
+  </si>
+  <si>
+    <t>category_code</t>
+  </si>
+  <si>
+    <t>VARCHAR(10) DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>類別代碼</t>
+  </si>
+  <si>
+    <t>lecturer_code</t>
+  </si>
+  <si>
+    <t>intro</t>
+  </si>
+  <si>
+    <t>課程簡介</t>
+  </si>
+  <si>
+    <t>outline</t>
+  </si>
+  <si>
+    <t>LONGTEXT DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>DATE NULL DEFAULT NULL</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>最後更新時間</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>TINYINT(1) NOT NULL DEFAULT 1</t>
+  </si>
+  <si>
+    <t>duration_minutes</t>
+  </si>
+  <si>
+    <t>INT NOT NULL DEFAULT 180</t>
+  </si>
+  <si>
+    <t>課程大綱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排課日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公開狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程時長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可讀可寫（限新增）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lecturers_name</t>
+  </si>
+  <si>
+    <t>lecturers_title</t>
+  </si>
+  <si>
+    <t>lecturers_sort_order</t>
+  </si>
+  <si>
+    <t>學員資料表 qahn_8_tpma_registrations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程資料表 qahn_8_tpma_courses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>講師資料表 qahn_8_tpma_lecturers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test_score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動寫入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>授課日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lecturers_code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程代碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>證書編號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>certificate_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receipt_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>receipt_status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收據狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動寫入、可查詢</t>
+  </si>
+  <si>
+    <t>收據管理系統</t>
+  </si>
+  <si>
+    <t>收據管理系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可讀可寫、自動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>繳費狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>remit_paid_at</t>
-  </si>
-  <si>
-    <t>DATETIME DEFAULT NULL</t>
-  </si>
-  <si>
-    <t>remit_amount</t>
-  </si>
-  <si>
-    <t>DECIMAL(10,2) DEFAULT NULL</t>
-  </si>
-  <si>
-    <t>匯款金額</t>
-  </si>
-  <si>
-    <t>VARCHAR(20) NOT NULL DEFAULT 'electronic'</t>
-  </si>
-  <si>
-    <t>VARCHAR(20) NOT NULL DEFAULT 'pending'</t>
-  </si>
-  <si>
-    <t>報名編號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名時間</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>承辦人姓名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>承辦人電子郵件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>資訊來源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>備註</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>匯款時間</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名狀態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>學員mail</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>學員手機</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司抬頭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司統編</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公司電話</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收據方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收件地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名管理系統</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>課程表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>課程管理系統</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>報名狀態查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>測驗卷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>資料匯入系統</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自動寫入</t>
-  </si>
-  <si>
-    <t>唯讀</t>
-  </si>
-  <si>
-    <t>只寫入</t>
-  </si>
-  <si>
-    <t>可讀可寫</t>
-  </si>
-  <si>
-    <t>唯讀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自動寫入、可查詢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>測驗成績</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VARCHAR(20) NOT NULL</t>
-  </si>
-  <si>
-    <t>INT NOT NULL DEFAULT 0</t>
-  </si>
-  <si>
-    <t>講師代碼</t>
-  </si>
-  <si>
-    <t>講師代碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>講師姓名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>職稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顯示順序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>course_code</t>
-  </si>
-  <si>
-    <t>VARCHAR(50) NOT NULL</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>課程類別</t>
-  </si>
-  <si>
-    <t>category_code</t>
-  </si>
-  <si>
-    <t>VARCHAR(10) DEFAULT NULL</t>
-  </si>
-  <si>
-    <t>類別代碼</t>
-  </si>
-  <si>
-    <t>lecturer_code</t>
-  </si>
-  <si>
-    <t>intro</t>
-  </si>
-  <si>
-    <t>課程簡介</t>
-  </si>
-  <si>
-    <t>outline</t>
-  </si>
-  <si>
-    <t>LONGTEXT DEFAULT NULL</t>
-  </si>
-  <si>
-    <t>DATE NULL DEFAULT NULL</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>最後更新時間</t>
-  </si>
-  <si>
-    <t>is_active</t>
-  </si>
-  <si>
-    <t>TINYINT(1) NOT NULL DEFAULT 1</t>
-  </si>
-  <si>
-    <t>duration_minutes</t>
-  </si>
-  <si>
-    <t>INT NOT NULL DEFAULT 180</t>
-  </si>
-  <si>
-    <t>課程大綱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排課日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公開狀態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>課程時長</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可讀可寫（限新增）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lecturers_name</t>
-  </si>
-  <si>
-    <t>lecturers_title</t>
-  </si>
-  <si>
-    <t>lecturers_sort_order</t>
-  </si>
-  <si>
-    <t>學員資料表 qahn_8_tpma_registrations</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>課程資料表 qahn_8_tpma_courses</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>講師資料表 qahn_8_tpma_lecturers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test_score</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自動寫入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>課程ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>授課日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lecturers_code</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>課程代碼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>證書編號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>certificate_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>receipt_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>receipt_status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收據狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>paid_status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>學員狀態</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -481,7 +588,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -527,6 +634,27 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -565,7 +693,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -581,6 +709,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -588,7 +722,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="39">
     <dxf>
       <font>
         <strike val="0"/>
@@ -597,6 +731,25 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="14"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
         <name val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -812,6 +965,25 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -949,6 +1121,25 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
         <name val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
@@ -1156,57 +1347,66 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="冠緯 謝" id="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" userId="544b8d222a0c7139" providerId="Windows Live"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}" name="表格4" displayName="表格4" ref="A40:J52" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <autoFilter ref="A40:J52" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1CDE2B07-2F75-402E-BED2-D95BF7C7A7E7}" name="英文欄位名稱" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{27B8293B-89CB-40EF-9105-6E5B6340931B}" name="資料型別" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{B5849207-37D2-4DDC-B8C7-68BED3ECFFC7}" name="中文名稱" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{FFF948C5-FDD2-43FF-B5CC-5C8327861541}" name="報名表" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{F4206593-7D6F-4FCE-A1E5-9B58643D8845}" name="報名狀態查詢" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{DFD16302-56A2-4F3C-B880-AF5525A17A2E}" name="課程表" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{6DB510A6-B6DE-4AED-942D-7625A70E05F3}" name="測驗卷" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{F021C9B4-DE4F-4C2E-BA16-466726236114}" name="報名管理系統" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{48383804-EB1C-436E-9445-1038B74B1698}" name="課程管理系統" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{0BEFD8DC-07A2-41ED-99E3-6F8334E18C65}" name="資料匯入系統" dataDxfId="24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}" name="表格4" displayName="表格4" ref="A41:K53" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+  <autoFilter ref="A41:K53" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{1CDE2B07-2F75-402E-BED2-D95BF7C7A7E7}" name="英文欄位名稱" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{27B8293B-89CB-40EF-9105-6E5B6340931B}" name="資料型別" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{B5849207-37D2-4DDC-B8C7-68BED3ECFFC7}" name="中文名稱" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{FFF948C5-FDD2-43FF-B5CC-5C8327861541}" name="報名表" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{F4206593-7D6F-4FCE-A1E5-9B58643D8845}" name="報名狀態查詢" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{DFD16302-56A2-4F3C-B880-AF5525A17A2E}" name="課程表" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{6DB510A6-B6DE-4AED-942D-7625A70E05F3}" name="測驗卷" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{F021C9B4-DE4F-4C2E-BA16-466726236114}" name="報名管理系統" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{48383804-EB1C-436E-9445-1038B74B1698}" name="課程管理系統" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{FA1E495B-DE70-49DE-9C95-568D0329E3B1}" name="收據管理系統" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{0BEFD8DC-07A2-41ED-99E3-6F8334E18C65}" name="資料匯入系統" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}" name="表格5" displayName="表格5" ref="A32:J37" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="A32:J37" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3BA59C37-9AA1-4EBB-9FE1-8D5C81CA5387}" name="英文欄位名稱" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{EB96F576-7E96-4FE3-9ADF-EB3D44092578}" name="資料型別" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{61269BC6-66D4-4D1C-90DD-38BA51F03DF1}" name="中文名稱" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{95AD6ED2-24A9-431F-ABD7-F2B93954BE9A}" name="報名表" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{592A5FCF-3241-4C87-86CB-40A6CC97EFE8}" name="報名狀態查詢" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{6C82C817-22D4-4CD6-9F4B-5CDD1D5161D0}" name="課程表" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{46D8AA77-F5EC-4234-AB84-28DC95DA6A62}" name="測驗卷" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{BFDA7469-533B-4D49-9C78-B5FA4ECBBE40}" name="報名管理系統" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{78D33096-EFE3-4576-BF38-4E4FBC62E2AF}" name="課程管理系統" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{96528DAF-BB86-4CB5-87DB-579EBAD1D1D3}" name="資料匯入系統" dataDxfId="12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}" name="表格5" displayName="表格5" ref="A33:K38" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="A33:K38" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{3BA59C37-9AA1-4EBB-9FE1-8D5C81CA5387}" name="英文欄位名稱" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{EB96F576-7E96-4FE3-9ADF-EB3D44092578}" name="資料型別" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{61269BC6-66D4-4D1C-90DD-38BA51F03DF1}" name="中文名稱" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{95AD6ED2-24A9-431F-ABD7-F2B93954BE9A}" name="報名表" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{592A5FCF-3241-4C87-86CB-40A6CC97EFE8}" name="報名狀態查詢" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{6C82C817-22D4-4CD6-9F4B-5CDD1D5161D0}" name="課程表" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{46D8AA77-F5EC-4234-AB84-28DC95DA6A62}" name="測驗卷" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{BFDA7469-533B-4D49-9C78-B5FA4ECBBE40}" name="報名管理系統" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{78D33096-EFE3-4576-BF38-4E4FBC62E2AF}" name="課程管理系統" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{53E64AA7-5C1B-4316-837F-5A96E9CB1936}" name="收據管理系統" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{96528DAF-BB86-4CB5-87DB-579EBAD1D1D3}" name="資料匯入系統" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}" name="表格6" displayName="表格6" ref="A2:J29" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A2:J29" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C047856F-978A-4D0E-8072-1384C375DEB2}" name="英文欄位名稱" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{37871FC5-A518-4945-9559-961D08C9AA59}" name="資料型別" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{B6C39498-99A7-4533-8905-47A79BD73E13}" name="中文名稱" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{BE05DC0B-6EB8-4976-B8A9-A6BC060673AE}" name="報名表" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{8D0EEA4D-C178-4C6A-BDB8-198C350930F9}" name="報名狀態查詢" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{63A4F83A-EEAF-468E-BC2D-EC5871399AA2}" name="課程表" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{A64470E9-5294-4EA1-90F6-D0608018E82D}" name="測驗卷" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{5B1DACFA-3A29-4844-947A-9D37498C8120}" name="報名管理系統" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{2CA52024-C050-4D81-A60C-4FC0346558DA}" name="課程管理系統" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}" name="表格6" displayName="表格6" ref="A2:K30" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A2:K30" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{C047856F-978A-4D0E-8072-1384C375DEB2}" name="英文欄位名稱" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{37871FC5-A518-4945-9559-961D08C9AA59}" name="資料型別" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{B6C39498-99A7-4533-8905-47A79BD73E13}" name="中文名稱" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{BE05DC0B-6EB8-4976-B8A9-A6BC060673AE}" name="報名表" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{8D0EEA4D-C178-4C6A-BDB8-198C350930F9}" name="報名狀態查詢" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{63A4F83A-EEAF-468E-BC2D-EC5871399AA2}" name="課程表" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{A64470E9-5294-4EA1-90F6-D0608018E82D}" name="測驗卷" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{5B1DACFA-3A29-4844-947A-9D37498C8120}" name="報名管理系統" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2CA52024-C050-4D81-A60C-4FC0346558DA}" name="課程管理系統" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{395A82D8-6082-4A18-A2EF-8D0AC7CF08F2}" name="收據管理系統" dataDxfId="1"/>
     <tableColumn id="10" xr3:uid="{150D65DA-0093-4FE5-819F-9B3F135A5694}" name="資料匯入系統" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1528,9 +1728,41 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D26" dT="2025-11-20T01:13:03.61" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{E8AEA38C-695D-476C-B251-A4AD4F985225}">
+    <text>自動寫入：未付款</text>
+  </threadedComment>
+  <threadedComment ref="E26" dT="2025-11-20T01:13:21.64" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{BB73BC85-84DA-4531-8D11-2FEC40B6C6D8}">
+    <text>自動寫入：待合帳</text>
+  </threadedComment>
+  <threadedComment ref="G26" dT="2025-11-20T01:14:09.82" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{9BAD3334-5BDE-4AD4-BD15-5631AF5FE627}">
+    <text>自動寫入：待發證</text>
+  </threadedComment>
+  <threadedComment ref="G27" dT="2025-11-21T08:23:23.77" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{C840BA3F-13DF-4C3B-B55C-EE68DB23CE7E}">
+    <text>自動寫入：待發證</text>
+  </threadedComment>
+  <threadedComment ref="A29" dT="2025-11-20T01:07:55.67" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{56566999-2D7A-450F-8573-8D9F8B382CCF}">
+    <text>1.待開立
+2.已自動
+3.已手動
+4.已寄出</text>
+  </threadedComment>
+  <threadedComment ref="D29" dT="2025-11-20T01:08:35.81" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{C6DC1EE6-FFFC-4540-8679-DE132156B117}">
+    <text>待開立</text>
+  </threadedComment>
+  <threadedComment ref="E29" dT="2025-11-20T01:08:50.44" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{EE33FCBE-1363-47FA-91CA-DAC4F880F21B}">
+    <text>自動寫入：已自動</text>
+  </threadedComment>
+  <threadedComment ref="J29" dT="2025-11-20T01:11:25.59" personId="{5050F281-6F20-4E09-88D5-0DFEB7B8EBD7}" id="{AB3E87E4-B2AE-4BF6-8465-D710692CC0A6}">
+    <text>自動寫入：已手動、已寄出</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34883627-C9A6-4AD2-B6FA-A28FEEF3DF7E}">
-  <dimension ref="A1:J52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34883627-C9A6-4AD2-B6FA-A28FEEF3DF7E}">
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" bestFit="1" customWidth="1"/>
@@ -1542,24 +1774,26 @@
     <col min="8" max="8" width="18.625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="24.5" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="17.75" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1567,31 +1801,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1599,16 +1836,16 @@
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1616,25 +1853,25 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1642,22 +1879,22 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1665,16 +1902,17 @@
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,22 +1920,23 @@
         <v>15</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1708,19 +1947,20 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1731,16 +1971,17 @@
         <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,16 +1992,17 @@
         <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1768,19 +2010,20 @@
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1788,19 +2031,20 @@
         <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -1808,19 +2052,20 @@
         <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1828,19 +2073,20 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1848,19 +2094,20 @@
         <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1868,19 +2115,20 @@
         <v>20</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -1888,39 +2136,41 @@
         <v>26</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -1928,19 +2178,20 @@
         <v>32</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -1948,19 +2199,20 @@
         <v>13</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -1968,19 +2220,20 @@
         <v>34</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -1988,19 +2241,20 @@
         <v>29</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -2011,531 +2265,572 @@
         <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="I44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="I45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="K48" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="K49" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I50" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="K50" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I34" s="2" t="s">
+      <c r="K51" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="I52" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>75</v>
+      <c r="I53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="3">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/TPMA 課程管理系統資料庫規劃.xlsx
+++ b/TPMA 課程管理系統資料庫規劃.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEB\tpma-course-registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CC97D7-C6A3-453D-9EC9-72FF710D6796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90105D30-8863-4D4E-A8DD-5305C1C65075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F77293A-3451-41FC-851F-0442166EED0A}"/>
   </bookViews>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="149">
   <si>
     <t>英文欄位名稱</t>
   </si>
@@ -582,13 +582,60 @@
   <si>
     <t>學員狀態</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程時間表 qahn_8_tpma_course_sessions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_datetime</t>
+  </si>
+  <si>
+    <t>課程資料表 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期時間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活躍狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文名稱</t>
+  </si>
+  <si>
+    <t>報名表</t>
+  </si>
+  <si>
+    <t>報名狀態查詢</t>
+  </si>
+  <si>
+    <t>課程表</t>
+  </si>
+  <si>
+    <t>測驗卷</t>
+  </si>
+  <si>
+    <t>報名管理系統</t>
+  </si>
+  <si>
+    <t>課程管理系統</t>
+  </si>
+  <si>
+    <t>資料匯入系統</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -633,12 +680,6 @@
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -693,7 +734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -709,20 +750,274 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="52">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1354,60 +1649,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}" name="表格4" displayName="表格4" ref="A41:K53" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}" name="表格4" displayName="表格4" ref="A41:K53" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A41:K53" xr:uid="{18CCF8D4-0E4F-4263-8844-2F3838A67C7A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1CDE2B07-2F75-402E-BED2-D95BF7C7A7E7}" name="英文欄位名稱" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{27B8293B-89CB-40EF-9105-6E5B6340931B}" name="資料型別" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{B5849207-37D2-4DDC-B8C7-68BED3ECFFC7}" name="中文名稱" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{FFF948C5-FDD2-43FF-B5CC-5C8327861541}" name="報名表" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{F4206593-7D6F-4FCE-A1E5-9B58643D8845}" name="報名狀態查詢" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{DFD16302-56A2-4F3C-B880-AF5525A17A2E}" name="課程表" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{6DB510A6-B6DE-4AED-942D-7625A70E05F3}" name="測驗卷" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{F021C9B4-DE4F-4C2E-BA16-466726236114}" name="報名管理系統" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{48383804-EB1C-436E-9445-1038B74B1698}" name="課程管理系統" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{FA1E495B-DE70-49DE-9C95-568D0329E3B1}" name="收據管理系統" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{0BEFD8DC-07A2-41ED-99E3-6F8334E18C65}" name="資料匯入系統" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{1CDE2B07-2F75-402E-BED2-D95BF7C7A7E7}" name="英文欄位名稱" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{27B8293B-89CB-40EF-9105-6E5B6340931B}" name="資料型別" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{B5849207-37D2-4DDC-B8C7-68BED3ECFFC7}" name="中文名稱" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{FFF948C5-FDD2-43FF-B5CC-5C8327861541}" name="報名表" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{F4206593-7D6F-4FCE-A1E5-9B58643D8845}" name="報名狀態查詢" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{DFD16302-56A2-4F3C-B880-AF5525A17A2E}" name="課程表" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{6DB510A6-B6DE-4AED-942D-7625A70E05F3}" name="測驗卷" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{F021C9B4-DE4F-4C2E-BA16-466726236114}" name="報名管理系統" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{48383804-EB1C-436E-9445-1038B74B1698}" name="課程管理系統" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{FA1E495B-DE70-49DE-9C95-568D0329E3B1}" name="收據管理系統" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{0BEFD8DC-07A2-41ED-99E3-6F8334E18C65}" name="資料匯入系統" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}" name="表格5" displayName="表格5" ref="A33:K38" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}" name="表格5" displayName="表格5" ref="A33:K38" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A33:K38" xr:uid="{BDCCC6B3-E18E-4C2D-8A3D-3556359F10E6}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{3BA59C37-9AA1-4EBB-9FE1-8D5C81CA5387}" name="英文欄位名稱" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{EB96F576-7E96-4FE3-9ADF-EB3D44092578}" name="資料型別" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{61269BC6-66D4-4D1C-90DD-38BA51F03DF1}" name="中文名稱" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{95AD6ED2-24A9-431F-ABD7-F2B93954BE9A}" name="報名表" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{592A5FCF-3241-4C87-86CB-40A6CC97EFE8}" name="報名狀態查詢" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{6C82C817-22D4-4CD6-9F4B-5CDD1D5161D0}" name="課程表" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{46D8AA77-F5EC-4234-AB84-28DC95DA6A62}" name="測驗卷" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{BFDA7469-533B-4D49-9C78-B5FA4ECBBE40}" name="報名管理系統" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{78D33096-EFE3-4576-BF38-4E4FBC62E2AF}" name="課程管理系統" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{53E64AA7-5C1B-4316-837F-5A96E9CB1936}" name="收據管理系統" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{96528DAF-BB86-4CB5-87DB-579EBAD1D1D3}" name="資料匯入系統" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{3BA59C37-9AA1-4EBB-9FE1-8D5C81CA5387}" name="英文欄位名稱" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{EB96F576-7E96-4FE3-9ADF-EB3D44092578}" name="資料型別" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{61269BC6-66D4-4D1C-90DD-38BA51F03DF1}" name="中文名稱" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{95AD6ED2-24A9-431F-ABD7-F2B93954BE9A}" name="報名表" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{592A5FCF-3241-4C87-86CB-40A6CC97EFE8}" name="報名狀態查詢" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{6C82C817-22D4-4CD6-9F4B-5CDD1D5161D0}" name="課程表" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{46D8AA77-F5EC-4234-AB84-28DC95DA6A62}" name="測驗卷" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{BFDA7469-533B-4D49-9C78-B5FA4ECBBE40}" name="報名管理系統" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{78D33096-EFE3-4576-BF38-4E4FBC62E2AF}" name="課程管理系統" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{53E64AA7-5C1B-4316-837F-5A96E9CB1936}" name="收據管理系統" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{96528DAF-BB86-4CB5-87DB-579EBAD1D1D3}" name="資料匯入系統" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}" name="表格6" displayName="表格6" ref="A2:K30" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}" name="表格6" displayName="表格6" ref="A2:K30" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A2:K30" xr:uid="{BB4E62AD-6331-4100-8A9C-0A5B82FD1676}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C047856F-978A-4D0E-8072-1384C375DEB2}" name="英文欄位名稱" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{37871FC5-A518-4945-9559-961D08C9AA59}" name="資料型別" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{B6C39498-99A7-4533-8905-47A79BD73E13}" name="中文名稱" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{BE05DC0B-6EB8-4976-B8A9-A6BC060673AE}" name="報名表" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{8D0EEA4D-C178-4C6A-BDB8-198C350930F9}" name="報名狀態查詢" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{63A4F83A-EEAF-468E-BC2D-EC5871399AA2}" name="課程表" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{A64470E9-5294-4EA1-90F6-D0608018E82D}" name="測驗卷" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{5B1DACFA-3A29-4844-947A-9D37498C8120}" name="報名管理系統" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2CA52024-C050-4D81-A60C-4FC0346558DA}" name="課程管理系統" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{395A82D8-6082-4A18-A2EF-8D0AC7CF08F2}" name="收據管理系統" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{150D65DA-0093-4FE5-819F-9B3F135A5694}" name="資料匯入系統" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C047856F-978A-4D0E-8072-1384C375DEB2}" name="英文欄位名稱" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{37871FC5-A518-4945-9559-961D08C9AA59}" name="資料型別" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{B6C39498-99A7-4533-8905-47A79BD73E13}" name="中文名稱" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{BE05DC0B-6EB8-4976-B8A9-A6BC060673AE}" name="報名表" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{8D0EEA4D-C178-4C6A-BDB8-198C350930F9}" name="報名狀態查詢" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{63A4F83A-EEAF-468E-BC2D-EC5871399AA2}" name="課程表" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{A64470E9-5294-4EA1-90F6-D0608018E82D}" name="測驗卷" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{5B1DACFA-3A29-4844-947A-9D37498C8120}" name="報名管理系統" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{2CA52024-C050-4D81-A60C-4FC0346558DA}" name="課程管理系統" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{395A82D8-6082-4A18-A2EF-8D0AC7CF08F2}" name="收據管理系統" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{150D65DA-0093-4FE5-819F-9B3F135A5694}" name="資料匯入系統" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2FE720F1-0568-4CCF-A218-DBF03F0919F8}" name="表格1" displayName="表格1" ref="A56:K61" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A56:K61" xr:uid="{2FE720F1-0568-4CCF-A218-DBF03F0919F8}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{0DAC8B9C-A3A7-4662-94A1-1C63975DB96A}" name="英文欄位名稱" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{D0A4F826-F927-4260-A56E-F7D5EB280B60}" name="資料型別" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{9BF12AF7-DC77-4C6E-A5E7-722B375DE6CB}" name="中文名稱" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{BAF53DE6-2FF4-49D7-940A-AA279CA786DA}" name="報名表" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{F7866A7A-75BE-43EB-8E8A-97D0EDC52855}" name="報名狀態查詢" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{21358DAD-9620-45F3-B4D4-9697363568B8}" name="課程表" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{719E9963-A082-4FDF-8CD8-F56D8932EB2C}" name="測驗卷" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{824B5B8F-F209-4EB9-B3C9-17F5BF69A800}" name="報名管理系統" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{8A5C5015-F3C2-4F21-90F5-49F3983E6434}" name="課程管理系統" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{5C6F7C15-728A-44CD-A9C0-1C8E7D455A1C}" name="收據管理系統" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{8B4F3156-B96D-4E33-936C-E18C103F59E0}" name="資料匯入系統" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1762,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34883627-C9A6-4AD2-B6FA-A28FEEF3DF7E}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" bestFit="1" customWidth="1"/>
@@ -2818,19 +3133,121 @@
         <v>73</v>
       </c>
     </row>
+    <row r="55" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="K61" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A55:K55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
-  <tableParts count="3">
+  <tableParts count="4">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/TPMA 課程管理系統資料庫規劃.xlsx
+++ b/TPMA 課程管理系統資料庫規劃.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEB\tpma-course-registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90105D30-8863-4D4E-A8DD-5305C1C65075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FCB31B-1047-4BC5-9FBC-B46E8C012B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0F77293A-3451-41FC-851F-0442166EED0A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0F77293A-3451-41FC-851F-0442166EED0A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -120,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="164">
   <si>
     <t>英文欄位名稱</t>
   </si>
@@ -629,13 +630,60 @@
   </si>
   <si>
     <t>資料匯入系統</t>
+  </si>
+  <si>
+    <t>已取消</t>
+  </si>
+  <si>
+    <t>待發證</t>
+  </si>
+  <si>
+    <t>已結訓</t>
+  </si>
+  <si>
+    <t>待付款</t>
+  </si>
+  <si>
+    <t>待核帳</t>
+  </si>
+  <si>
+    <t>已開待寄（自）</t>
+  </si>
+  <si>
+    <t>已開待寄（手）</t>
+  </si>
+  <si>
+    <t>已開已寄（自）</t>
+  </si>
+  <si>
+    <t>已開已寄（手）</t>
+  </si>
+  <si>
+    <t>待測驗</t>
+  </si>
+  <si>
+    <t>已測驗</t>
+  </si>
+  <si>
+    <t>電子收據</t>
+  </si>
+  <si>
+    <t>紙本收據</t>
+  </si>
+  <si>
+    <t>🔒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -696,8 +744,37 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MingLiU"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -707,6 +784,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,7 +829,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -756,15 +851,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -772,6 +882,158 @@
   <dxfs count="52">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -791,6 +1053,44 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -810,7 +1110,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -826,197 +1126,7 @@
         <charset val="136"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1709,20 +1819,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2FE720F1-0568-4CCF-A218-DBF03F0919F8}" name="表格1" displayName="表格1" ref="A56:K61" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2FE720F1-0568-4CCF-A218-DBF03F0919F8}" name="表格1" displayName="表格1" ref="A56:K61" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A56:K61" xr:uid="{2FE720F1-0568-4CCF-A218-DBF03F0919F8}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0DAC8B9C-A3A7-4662-94A1-1C63975DB96A}" name="英文欄位名稱" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D0A4F826-F927-4260-A56E-F7D5EB280B60}" name="資料型別" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{9BF12AF7-DC77-4C6E-A5E7-722B375DE6CB}" name="中文名稱" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{BAF53DE6-2FF4-49D7-940A-AA279CA786DA}" name="報名表" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{F7866A7A-75BE-43EB-8E8A-97D0EDC52855}" name="報名狀態查詢" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{21358DAD-9620-45F3-B4D4-9697363568B8}" name="課程表" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{719E9963-A082-4FDF-8CD8-F56D8932EB2C}" name="測驗卷" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{824B5B8F-F209-4EB9-B3C9-17F5BF69A800}" name="報名管理系統" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{8A5C5015-F3C2-4F21-90F5-49F3983E6434}" name="課程管理系統" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{5C6F7C15-728A-44CD-A9C0-1C8E7D455A1C}" name="收據管理系統" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{8B4F3156-B96D-4E33-936C-E18C103F59E0}" name="資料匯入系統" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{0DAC8B9C-A3A7-4662-94A1-1C63975DB96A}" name="英文欄位名稱" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{D0A4F826-F927-4260-A56E-F7D5EB280B60}" name="資料型別" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{9BF12AF7-DC77-4C6E-A5E7-722B375DE6CB}" name="中文名稱" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{BAF53DE6-2FF4-49D7-940A-AA279CA786DA}" name="報名表" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{F7866A7A-75BE-43EB-8E8A-97D0EDC52855}" name="報名狀態查詢" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{21358DAD-9620-45F3-B4D4-9697363568B8}" name="課程表" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{719E9963-A082-4FDF-8CD8-F56D8932EB2C}" name="測驗卷" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{824B5B8F-F209-4EB9-B3C9-17F5BF69A800}" name="報名管理系統" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{8A5C5015-F3C2-4F21-90F5-49F3983E6434}" name="課程管理系統" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{5C6F7C15-728A-44CD-A9C0-1C8E7D455A1C}" name="收據管理系統" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{8B4F3156-B96D-4E33-936C-E18C103F59E0}" name="資料匯入系統" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2078,7 +2188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34883627-C9A6-4AD2-B6FA-A28FEEF3DF7E}">
   <dimension ref="A1:K61"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="19.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.625" style="1" hidden="1" customWidth="1"/>
@@ -2093,22 +2203,22 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2143,7 +2253,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2160,7 +2270,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -2186,7 +2296,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2209,7 +2319,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2227,7 +2337,7 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2251,7 +2361,7 @@
       </c>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -2275,7 +2385,7 @@
       </c>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -2296,7 +2406,7 @@
       </c>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -2317,7 +2427,7 @@
       </c>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -2338,7 +2448,7 @@
       </c>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -2359,7 +2469,7 @@
       </c>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -2380,7 +2490,7 @@
       </c>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -2401,7 +2511,7 @@
       </c>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -2422,7 +2532,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2443,7 +2553,7 @@
       </c>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2464,7 +2574,7 @@
       </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>123</v>
       </c>
@@ -2485,7 +2595,7 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -2506,7 +2616,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -2527,7 +2637,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
@@ -2548,7 +2658,7 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -2569,7 +2679,7 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -2587,7 +2697,7 @@
       </c>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>132</v>
       </c>
@@ -2605,7 +2715,7 @@
       </c>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -2623,7 +2733,7 @@
       </c>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11">
       <c r="A26" s="5" t="s">
         <v>133</v>
       </c>
@@ -2647,7 +2757,7 @@
       </c>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11">
       <c r="A27" s="5" t="s">
         <v>124</v>
       </c>
@@ -2662,7 +2772,7 @@
       </c>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
         <v>115</v>
       </c>
@@ -2680,7 +2790,7 @@
       </c>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
         <v>125</v>
       </c>
@@ -2701,7 +2811,7 @@
       </c>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>122</v>
       </c>
@@ -2719,22 +2829,22 @@
       </c>
       <c r="K30" s="2"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:11">
+      <c r="A32" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -2769,7 +2879,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
         <v>2</v>
       </c>
@@ -2786,7 +2896,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11">
       <c r="A35" s="1" t="s">
         <v>119</v>
       </c>
@@ -2803,7 +2913,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11">
       <c r="A36" s="1" t="s">
         <v>109</v>
       </c>
@@ -2820,7 +2930,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11">
       <c r="A37" s="1" t="s">
         <v>110</v>
       </c>
@@ -2837,7 +2947,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11">
       <c r="A38" s="1" t="s">
         <v>111</v>
       </c>
@@ -2854,22 +2964,22 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:11">
+      <c r="A40" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -2904,7 +3014,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11">
       <c r="A42" s="1" t="s">
         <v>2</v>
       </c>
@@ -2921,7 +3031,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -2938,7 +3048,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
         <v>10</v>
       </c>
@@ -2961,7 +3071,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
         <v>87</v>
       </c>
@@ -2979,7 +3089,7 @@
       </c>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11">
       <c r="A46" s="1" t="s">
         <v>89</v>
       </c>
@@ -2996,7 +3106,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
@@ -3013,7 +3123,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
         <v>93</v>
       </c>
@@ -3033,7 +3143,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
         <v>95</v>
       </c>
@@ -3053,7 +3163,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
         <v>14</v>
       </c>
@@ -3076,7 +3186,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11">
       <c r="A51" s="1" t="s">
         <v>98</v>
       </c>
@@ -3093,7 +3203,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11">
       <c r="A52" s="1" t="s">
         <v>100</v>
       </c>
@@ -3113,7 +3223,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11">
       <c r="A53" s="1" t="s">
         <v>102</v>
       </c>
@@ -3133,102 +3243,102 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+    <row r="55" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A55" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-    </row>
-    <row r="56" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+    </row>
+    <row r="56" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A56" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J56" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="K56" s="8" t="s">
+      <c r="K56" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:11">
+      <c r="A57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9" t="s">
+      <c r="B57" s="8"/>
+      <c r="C57" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
+    <row r="58" spans="1:11">
+      <c r="A58" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9" t="s">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8" t="s">
         <v>137</v>
       </c>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:11">
+      <c r="A59" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9" t="s">
+      <c r="B59" s="8"/>
+      <c r="C59" s="8" t="s">
         <v>138</v>
       </c>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+    <row r="60" spans="1:11">
+      <c r="A60" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9" t="s">
+      <c r="B60" s="8"/>
+      <c r="C60" s="8" t="s">
         <v>139</v>
       </c>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:11">
+      <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9" t="s">
+      <c r="B61" s="8"/>
+      <c r="C61" s="8" t="s">
         <v>140</v>
       </c>
       <c r="K61" s="2"/>
@@ -3250,4 +3360,231 @@
     <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51E2FF4-4A49-451C-A100-83673489364B}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="17.25">
+      <c r="A8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="17.25">
+      <c r="A9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="17.25">
+      <c r="A10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J10" s="11"/>
+      <c r="K10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="17.25">
+      <c r="A12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="M13" s="11"/>
+      <c r="N13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="17.25">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="N14" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>